--- a/dados/excel/quadro_escolaridade_por_ano.xlsx
+++ b/dados/excel/quadro_escolaridade_por_ano.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>13</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>406047.57</v>
+        <v>453140.26</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>4319.655</v>
+        <v>4315.621523809524</v>
       </c>
     </row>
     <row r="43">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>598</v>
+        <v>669</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>74</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>3584796.65</v>
+        <v>4089212.15</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>5994.643227424749</v>
+        <v>6112.424738415545</v>
       </c>
     </row>
     <row r="44">
@@ -1749,16 +1749,16 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2419</v>
+        <v>2717</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>12719337.17</v>
+        <v>14306708.67</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>5258.097217858619</v>
+        <v>5265.627040853883</v>
       </c>
     </row>
     <row r="45">
@@ -1771,16 +1771,16 @@
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>22</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1234757.25</v>
+        <v>1388202.44</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>6567.857712765957</v>
+        <v>6674.050192307692</v>
       </c>
     </row>
     <row r="46">
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>31615</v>
+        <v>35508</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>3815</v>
+        <v>3877</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>170818062.25</v>
+        <v>193574682.34</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>5403.070132848332</v>
+        <v>5451.579428297849</v>
       </c>
     </row>
     <row r="47">
@@ -1815,16 +1815,16 @@
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>8111</v>
+        <v>9116</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1477</v>
+        <v>1542</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>18016059.45</v>
+        <v>20421366.83</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>2221.188441622488</v>
+        <v>2240.167489030276</v>
       </c>
     </row>
     <row r="48">
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>59331</v>
+        <v>67071</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>8186</v>
+        <v>8546</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>493049289.48</v>
+        <v>560069772.55</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8310.14628912373</v>
+        <v>8350.401403736338</v>
       </c>
     </row>
     <row r="49">
@@ -1859,16 +1859,16 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>18720</v>
+        <v>20778</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>2086</v>
+        <v>2103</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>253722914.81</v>
+        <v>285913590.39</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>13553.5745090812</v>
+        <v>13760.39996101646</v>
       </c>
     </row>
     <row r="50">
@@ -1881,16 +1881,16 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>1108</v>
+        <v>1236</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>114</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>19888581.95</v>
+        <v>22492217.63</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>17949.98370938628</v>
+        <v>18197.58707928802</v>
       </c>
     </row>
     <row r="51">
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>5174027.05</v>
+        <v>5876200.19</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>19378.37846441947</v>
+        <v>19718.79258389262</v>
       </c>
     </row>
   </sheetData>
